--- a/R_Codes/DataSummary/All_Prokaryotes/Sample_name/All_Prokaryotes_Summary_Domain_by_Sample_name.xlsx
+++ b/R_Codes/DataSummary/All_Prokaryotes/Sample_name/All_Prokaryotes_Summary_Domain_by_Sample_name.xlsx
@@ -391,10 +391,10 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>87.3783977455557</v>
+        <v>87.3737726430094</v>
       </c>
       <c r="D2" t="n">
-        <v>0.239431305925468</v>
+        <v>0.23961303249793</v>
       </c>
     </row>
     <row r="3">
@@ -405,10 +405,10 @@
         <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>12.6216022544439</v>
+        <v>12.6262273569915</v>
       </c>
       <c r="D3" t="n">
-        <v>0.175765310603475</v>
+        <v>0.175893244904619</v>
       </c>
     </row>
   </sheetData>
@@ -444,10 +444,10 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>69.5591259270452</v>
+        <v>68.8890985628643</v>
       </c>
       <c r="D2" t="n">
-        <v>0.545793282395704</v>
+        <v>0.55280325168445</v>
       </c>
     </row>
     <row r="3">
@@ -458,10 +458,10 @@
         <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>30.4408740729543</v>
+        <v>31.1109014371351</v>
       </c>
       <c r="D3" t="n">
-        <v>0.772639844872641</v>
+        <v>0.79239593974379</v>
       </c>
     </row>
   </sheetData>
@@ -497,10 +497,10 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>74.3463355796281</v>
+        <v>74.3480115595076</v>
       </c>
       <c r="D2" t="n">
-        <v>0.141171938920425</v>
+        <v>0.141310157320179</v>
       </c>
     </row>
     <row r="3">
@@ -511,10 +511,10 @@
         <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>25.6536644203717</v>
+        <v>25.6519884404912</v>
       </c>
       <c r="D3" t="n">
-        <v>0.159810419054134</v>
+        <v>0.159781326491811</v>
       </c>
     </row>
   </sheetData>
